--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122571097</v>
+        <v>122570909</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>92113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592615</v>
+        <v>592664</v>
       </c>
       <c r="R2" t="n">
-        <v>6395350</v>
+        <v>6395349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +764,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122570909</v>
+        <v>122571097</v>
       </c>
       <c r="B3" t="n">
-        <v>92100</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592664</v>
+        <v>592615</v>
       </c>
       <c r="R3" t="n">
-        <v>6395349</v>
+        <v>6395350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,13 +875,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570915</v>
+        <v>122570978</v>
       </c>
       <c r="B4" t="n">
-        <v>105330</v>
+        <v>95009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,29 +920,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592664</v>
+        <v>592725</v>
       </c>
       <c r="R4" t="n">
-        <v>6395349</v>
+        <v>6395331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570978</v>
+        <v>122570915</v>
       </c>
       <c r="B5" t="n">
-        <v>94996</v>
+        <v>105343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,25 +1027,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592725</v>
+        <v>592664</v>
       </c>
       <c r="R5" t="n">
-        <v>6395331</v>
+        <v>6395349</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122570909</v>
+        <v>122571097</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592664</v>
+        <v>592615</v>
       </c>
       <c r="R2" t="n">
-        <v>6395349</v>
+        <v>6395350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,13 +761,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122571097</v>
+        <v>122570915</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>105346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592615</v>
+        <v>592664</v>
       </c>
       <c r="R3" t="n">
-        <v>6395350</v>
+        <v>6395349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,17 +876,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570978</v>
+        <v>122570909</v>
       </c>
       <c r="B4" t="n">
-        <v>95009</v>
+        <v>92114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,27 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592725</v>
+        <v>592664</v>
       </c>
       <c r="R4" t="n">
-        <v>6395331</v>
+        <v>6395349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570915</v>
+        <v>122570978</v>
       </c>
       <c r="B5" t="n">
-        <v>105343</v>
+        <v>95011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,29 +1031,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592664</v>
+        <v>592725</v>
       </c>
       <c r="R5" t="n">
-        <v>6395349</v>
+        <v>6395331</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122571097</v>
+        <v>122570909</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>92114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592615</v>
+        <v>592664</v>
       </c>
       <c r="R2" t="n">
-        <v>6395350</v>
+        <v>6395349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +764,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122570915</v>
+        <v>122571097</v>
       </c>
       <c r="B3" t="n">
-        <v>105346</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592664</v>
+        <v>592615</v>
       </c>
       <c r="R3" t="n">
-        <v>6395349</v>
+        <v>6395350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,13 +875,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570909</v>
+        <v>122570978</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +920,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592664</v>
+        <v>592725</v>
       </c>
       <c r="R4" t="n">
-        <v>6395349</v>
+        <v>6395331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570978</v>
+        <v>122570915</v>
       </c>
       <c r="B5" t="n">
-        <v>95011</v>
+        <v>105346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,25 +1027,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592725</v>
+        <v>592664</v>
       </c>
       <c r="R5" t="n">
-        <v>6395331</v>
+        <v>6395349</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122570909</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122571097</v>
+        <v>122570978</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>95012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +801,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592615</v>
+        <v>592725</v>
       </c>
       <c r="R3" t="n">
-        <v>6395350</v>
+        <v>6395331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,17 +871,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570978</v>
+        <v>122571097</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,31 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592725</v>
+        <v>592615</v>
       </c>
       <c r="R4" t="n">
-        <v>6395331</v>
+        <v>6395350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,13 +982,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>122570915</v>
       </c>
       <c r="B5" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122570909</v>
+        <v>122570978</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>95015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592664</v>
+        <v>592725</v>
       </c>
       <c r="R2" t="n">
-        <v>6395349</v>
+        <v>6395331</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122570978</v>
+        <v>122570915</v>
       </c>
       <c r="B3" t="n">
-        <v>95012</v>
+        <v>105350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,25 +798,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592725</v>
+        <v>592664</v>
       </c>
       <c r="R3" t="n">
-        <v>6395331</v>
+        <v>6395349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122571097</v>
+        <v>122570909</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>92118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +905,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592615</v>
+        <v>592664</v>
       </c>
       <c r="R4" t="n">
-        <v>6395350</v>
+        <v>6395349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,17 +982,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570915</v>
+        <v>122571097</v>
       </c>
       <c r="B5" t="n">
-        <v>105347</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592664</v>
+        <v>592615</v>
       </c>
       <c r="R5" t="n">
-        <v>6395349</v>
+        <v>6395350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,13 +1093,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122570978</v>
+        <v>122570909</v>
       </c>
       <c r="B2" t="n">
-        <v>95015</v>
+        <v>92118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592725</v>
+        <v>592664</v>
       </c>
       <c r="R2" t="n">
-        <v>6395331</v>
+        <v>6395349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122570915</v>
+        <v>122571097</v>
       </c>
       <c r="B3" t="n">
-        <v>105350</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592664</v>
+        <v>592615</v>
       </c>
       <c r="R3" t="n">
-        <v>6395349</v>
+        <v>6395350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,13 +875,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570909</v>
+        <v>122570915</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>105350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +920,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1007,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122571097</v>
+        <v>122570978</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>95015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,35 +1027,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592615</v>
+        <v>592725</v>
       </c>
       <c r="R5" t="n">
-        <v>6395350</v>
+        <v>6395331</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1097,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122570909</v>
+        <v>122570978</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>95118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592664</v>
+        <v>592725</v>
       </c>
       <c r="R2" t="n">
-        <v>6395349</v>
+        <v>6395331</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,7 +785,7 @@
         <v>122571097</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570915</v>
+        <v>122570909</v>
       </c>
       <c r="B4" t="n">
-        <v>105350</v>
+        <v>92221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570978</v>
+        <v>122570915</v>
       </c>
       <c r="B5" t="n">
-        <v>95015</v>
+        <v>105453</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,25 +1027,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592725</v>
+        <v>592664</v>
       </c>
       <c r="R5" t="n">
-        <v>6395331</v>
+        <v>6395349</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122570978</v>
       </c>
       <c r="B2" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570909</v>
+        <v>122570915</v>
       </c>
       <c r="B4" t="n">
-        <v>92221</v>
+        <v>105461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570915</v>
+        <v>122570909</v>
       </c>
       <c r="B5" t="n">
-        <v>105453</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,31 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122570978</v>
+        <v>122570915</v>
       </c>
       <c r="B2" t="n">
-        <v>95126</v>
+        <v>105461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592725</v>
+        <v>592664</v>
       </c>
       <c r="R2" t="n">
-        <v>6395331</v>
+        <v>6395349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122571097</v>
+        <v>122570909</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592615</v>
+        <v>592664</v>
       </c>
       <c r="R3" t="n">
-        <v>6395350</v>
+        <v>6395349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,17 +875,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570915</v>
+        <v>122570978</v>
       </c>
       <c r="B4" t="n">
-        <v>105461</v>
+        <v>95126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,29 +916,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592664</v>
+        <v>592725</v>
       </c>
       <c r="R4" t="n">
-        <v>6395349</v>
+        <v>6395331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570909</v>
+        <v>122571097</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592664</v>
+        <v>592615</v>
       </c>
       <c r="R5" t="n">
-        <v>6395349</v>
+        <v>6395350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,13 +1093,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122570915</v>
+        <v>122570909</v>
       </c>
       <c r="B2" t="n">
-        <v>105461</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122570909</v>
+        <v>122570978</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>95128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +805,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592664</v>
+        <v>592725</v>
       </c>
       <c r="R3" t="n">
-        <v>6395349</v>
+        <v>6395331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122570978</v>
+        <v>122571097</v>
       </c>
       <c r="B4" t="n">
-        <v>95126</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592725</v>
+        <v>592615</v>
       </c>
       <c r="R4" t="n">
-        <v>6395331</v>
+        <v>6395350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,13 +982,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122571097</v>
+        <v>122570915</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,35 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592615</v>
+        <v>592664</v>
       </c>
       <c r="R5" t="n">
-        <v>6395350</v>
+        <v>6395349</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1097,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1742-2025 artfynd.xlsx
+++ b/artfynd/A 1742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122570909</v>
+        <v>122570915</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>105463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122570978</v>
+        <v>122571097</v>
       </c>
       <c r="B3" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592725</v>
+        <v>592615</v>
       </c>
       <c r="R3" t="n">
-        <v>6395331</v>
+        <v>6395350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,13 +872,17 @@
           <t>2025-02-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre bohål i 2 aspar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122571097</v>
+        <v>122570978</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>95128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592615</v>
+        <v>592725</v>
       </c>
       <c r="R4" t="n">
-        <v>6395350</v>
+        <v>6395331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,17 +983,13 @@
           <t>2025-02-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre bohål i 2 aspar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122570915</v>
+        <v>122570909</v>
       </c>
       <c r="B5" t="n">
-        <v>105463</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,31 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
